--- a/тестовые_отчёты/тестовые_отчёты/Отдел_кадров_отчёт.xlsx
+++ b/тестовые_отчёты/тестовые_отчёты/Отдел_кадров_отчёт.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,41 +413,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>№ п/п</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Наименование (факт)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Категория (внутр)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Сумма, руб</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Дата операции</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Подразделение</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Статус</t>
         </is>
@@ -471,20 +459,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>кофе</t>
+          <t>бензин</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>чай_кофе</t>
+          <t>транспорт</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15413</v>
+        <v>10874</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>08.05.2026</t>
+          <t>09.06.2026</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -494,7 +482,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ожидает</t>
+          <t>оплачено</t>
         </is>
       </c>
     </row>
@@ -504,20 +492,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>кресла</t>
+          <t>бумага А4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>мебель</t>
+          <t>бумага</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10083</v>
+        <v>44060</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>14.05.2026</t>
+          <t>14.06.2026</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -537,20 +525,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>бумага</t>
+          <t>расходники принтера</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>бумага</t>
+          <t>картриджи</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>42871</v>
+        <v>42171</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>09.05.2026</t>
+          <t>23.05.2026</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -570,20 +558,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>хозтовары</t>
+          <t>семинары</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>хозтовары</t>
+          <t>обучение</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>24432</v>
+        <v>10075</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>27.04.2026</t>
+          <t>12.06.2026</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -593,7 +581,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ожидает</t>
+          <t>оплачено</t>
         </is>
       </c>
     </row>
@@ -603,20 +591,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>курсы</t>
+          <t>канцтовары</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>обучение</t>
+          <t>канцтовары</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>35374</v>
+        <v>1305</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>25.04.2026</t>
+          <t>20.06.2026</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,20 +624,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>канцелярия</t>
+          <t>расходники принтера</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>канцтовары</t>
+          <t>картриджи</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>49562</v>
+        <v>10854</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>04.05.2026</t>
+          <t>07.06.2026</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,7 +647,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ожидает</t>
+          <t>оплачено</t>
         </is>
       </c>
     </row>
@@ -669,20 +657,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>часы</t>
+          <t>бензин</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>краснухи</t>
+          <t>транспорт</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>44377</v>
+        <v>44538</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>02.05.2026</t>
+          <t>07.06.2026</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -702,20 +690,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>лев в клетке</t>
+          <t>тренинги</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>краснухи</t>
+          <t>обучение</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>43306</v>
+        <v>38009</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11.05.2026</t>
+          <t>17.06.2026</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -735,20 +723,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>расходники принтера</t>
+          <t>салфетки</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>картриджи</t>
+          <t>хозтовары</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4450</v>
+        <v>13613</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>01.05.2026</t>
+          <t>20.06.2026</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -768,20 +756,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>картриджи</t>
+          <t>бумага А4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>картриджи</t>
+          <t>бумага</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>48560</v>
+        <v>38983</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>13.05.2026</t>
+          <t>05.06.2026</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -801,20 +789,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>бытовая химия</t>
+          <t>бумага</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>хозтовары</t>
+          <t>бумага</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>22308</v>
+        <v>15501</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>30.04.2026</t>
+          <t>19.06.2026</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -824,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ожидает</t>
+          <t>оплачено</t>
         </is>
       </c>
     </row>
@@ -834,20 +822,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>часы</t>
+          <t>бензин</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>краснухи</t>
+          <t>транспорт</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>5188</v>
+        <v>33158</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>03.05.2026</t>
+          <t>05.06.2026</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -857,7 +845,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>оплачено</t>
+          <t>ожидает</t>
         </is>
       </c>
     </row>
@@ -867,20 +855,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>кофе</t>
+          <t>картриджи</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>чай_кофе</t>
+          <t>картриджи</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>44736</v>
+        <v>7448</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>26.04.2026</t>
+          <t>07.06.2026</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -890,7 +878,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>оплачено</t>
+          <t>ожидает</t>
         </is>
       </c>
     </row>
@@ -900,20 +888,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ГСМ</t>
+          <t>канцтовары</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>транспорт</t>
+          <t>канцтовары</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>21616</v>
+        <v>35068</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>03.05.2026</t>
+          <t>19.06.2026</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -942,11 +930,11 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>6987</v>
+        <v>7030</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>23.04.2026</t>
+          <t>07.06.2026</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -966,20 +954,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>печенье к чаю</t>
+          <t>канцелярия</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>чай_кофе</t>
+          <t>канцтовары</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>5191</v>
+        <v>27712</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>17.05.2026</t>
+          <t>19.06.2026</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -989,469 +977,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>оплачено</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>чай</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>чай_кофе</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>23909</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>17.05.2026</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Отдел_кадров</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>оплачено</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>салфетки</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>хозтовары</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>36635</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>09.05.2026</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Отдел_кадров</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
           <t>ожидает</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>расходники принтера</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>картриджи</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>14808</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>15.05.2026</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Отдел_кадров</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>оплачено</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>курсы</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>обучение</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>8963</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>07.05.2026</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Отдел_кадров</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>ожидает</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>канцелярия</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>канцтовары</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>15069</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>18.05.2026</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Отдел_кадров</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ожидает</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>офисные товары</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>канцтовары</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>9275</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>02.05.2026</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Отдел_кадров</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>оплачено</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>напитки</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>чай_кофе</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>48735</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>26.04.2026</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Отдел_кадров</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>оплачено</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>напитки</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>чай_кофе</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>44717</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>11.05.2026</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Отдел_кадров</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>оплачено</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>кресла</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>мебель</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>16297</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>05.05.2026</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Отдел_кадров</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>оплачено</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>лев в клетке</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>краснухи</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>9877</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>20.04.2026</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Отдел_кадров</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>ожидает</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>часы</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>краснухи</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>43616</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>15.05.2026</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Отдел_кадров</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>оплачено</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>курсы</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>обучение</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>11863</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>15.05.2026</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Отдел_кадров</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>ожидает</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>лев в клетке</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>краснухи</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>36187</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>26.04.2026</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Отдел_кадров</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>ожидает</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>офисная бумага</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>бумага</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>40689</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>07.05.2026</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Отдел_кадров</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>оплачено</t>
         </is>
       </c>
     </row>
